--- a/ig/ch-elm/ch-elm-results-to-foph-patient-name-representation.xlsx
+++ b/ig/ch-elm/ch-elm-results-to-foph-patient-name-representation.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1641" uniqueCount="834">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1645" uniqueCount="836">
   <si>
     <t>Property</t>
   </si>
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.13.1</t>
+    <t>1.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T11:21:00+00:00</t>
+    <t>2026-05-26T14:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -429,6 +429,12 @@
   </si>
   <si>
     <t>Salmonella sp identified in Specimen by Organism specific culture</t>
+  </si>
+  <si>
+    <t>17576-0</t>
+  </si>
+  <si>
+    <t>Shigella sp identified in Specimen by Organism specific culture</t>
   </si>
   <si>
     <t>17735-2</t>
@@ -2790,7 +2796,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E382"/>
+  <dimension ref="A1:E383"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -3573,7 +3579,7 @@
         <v>38</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E52" s="2"/>
     </row>
@@ -3588,7 +3594,7 @@
         <v>38</v>
       </c>
       <c r="D53" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E53" s="2"/>
     </row>
@@ -3603,7 +3609,7 @@
         <v>38</v>
       </c>
       <c r="D54" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E54" s="2"/>
     </row>
@@ -3618,7 +3624,7 @@
         <v>38</v>
       </c>
       <c r="D55" t="s" s="2">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="E55" s="2"/>
     </row>
@@ -3648,7 +3654,7 @@
         <v>38</v>
       </c>
       <c r="D57" t="s" s="2">
-        <v>39</v>
+        <v>119</v>
       </c>
       <c r="E57" s="2"/>
     </row>
@@ -3678,7 +3684,7 @@
         <v>38</v>
       </c>
       <c r="D59" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E59" s="2"/>
     </row>
@@ -3708,7 +3714,7 @@
         <v>38</v>
       </c>
       <c r="D61" t="s" s="2">
-        <v>39</v>
+        <v>119</v>
       </c>
       <c r="E61" s="2"/>
     </row>
@@ -3723,7 +3729,7 @@
         <v>38</v>
       </c>
       <c r="D62" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E62" s="2"/>
     </row>
@@ -3738,7 +3744,7 @@
         <v>38</v>
       </c>
       <c r="D63" t="s" s="2">
-        <v>39</v>
+        <v>119</v>
       </c>
       <c r="E63" s="2"/>
     </row>
@@ -3828,7 +3834,7 @@
         <v>38</v>
       </c>
       <c r="D69" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E69" s="2"/>
     </row>
@@ -3873,7 +3879,7 @@
         <v>38</v>
       </c>
       <c r="D72" t="s" s="2">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="E72" s="2"/>
     </row>
@@ -3888,7 +3894,7 @@
         <v>38</v>
       </c>
       <c r="D73" t="s" s="2">
-        <v>39</v>
+        <v>119</v>
       </c>
       <c r="E73" s="2"/>
     </row>
@@ -3918,7 +3924,7 @@
         <v>38</v>
       </c>
       <c r="D75" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E75" s="2"/>
     </row>
@@ -3933,7 +3939,7 @@
         <v>38</v>
       </c>
       <c r="D76" t="s" s="2">
-        <v>39</v>
+        <v>119</v>
       </c>
       <c r="E76" s="2"/>
     </row>
@@ -3963,7 +3969,7 @@
         <v>38</v>
       </c>
       <c r="D78" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E78" s="2"/>
     </row>
@@ -3993,7 +3999,7 @@
         <v>38</v>
       </c>
       <c r="D80" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E80" s="2"/>
     </row>
@@ -4008,7 +4014,7 @@
         <v>38</v>
       </c>
       <c r="D81" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E81" s="2"/>
     </row>
@@ -4023,7 +4029,7 @@
         <v>38</v>
       </c>
       <c r="D82" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E82" s="2"/>
     </row>
@@ -4053,7 +4059,7 @@
         <v>38</v>
       </c>
       <c r="D84" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E84" s="2"/>
     </row>
@@ -4068,7 +4074,7 @@
         <v>38</v>
       </c>
       <c r="D85" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E85" s="2"/>
     </row>
@@ -4158,7 +4164,7 @@
         <v>38</v>
       </c>
       <c r="D91" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E91" s="2"/>
     </row>
@@ -4173,7 +4179,7 @@
         <v>38</v>
       </c>
       <c r="D92" t="s" s="2">
-        <v>39</v>
+        <v>119</v>
       </c>
       <c r="E92" s="2"/>
     </row>
@@ -4203,7 +4209,7 @@
         <v>38</v>
       </c>
       <c r="D94" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E94" s="2"/>
     </row>
@@ -4233,7 +4239,7 @@
         <v>38</v>
       </c>
       <c r="D96" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E96" s="2"/>
     </row>
@@ -4248,7 +4254,7 @@
         <v>38</v>
       </c>
       <c r="D97" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E97" s="2"/>
     </row>
@@ -4278,7 +4284,7 @@
         <v>38</v>
       </c>
       <c r="D99" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E99" s="2"/>
     </row>
@@ -4398,7 +4404,7 @@
         <v>38</v>
       </c>
       <c r="D107" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E107" s="2"/>
     </row>
@@ -4413,7 +4419,7 @@
         <v>38</v>
       </c>
       <c r="D108" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E108" s="2"/>
     </row>
@@ -4428,7 +4434,7 @@
         <v>38</v>
       </c>
       <c r="D109" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E109" s="2"/>
     </row>
@@ -4443,7 +4449,7 @@
         <v>38</v>
       </c>
       <c r="D110" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E110" s="2"/>
     </row>
@@ -4458,7 +4464,7 @@
         <v>38</v>
       </c>
       <c r="D111" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E111" s="2"/>
     </row>
@@ -4473,7 +4479,7 @@
         <v>38</v>
       </c>
       <c r="D112" t="s" s="2">
-        <v>39</v>
+        <v>119</v>
       </c>
       <c r="E112" s="2"/>
     </row>
@@ -4488,7 +4494,7 @@
         <v>38</v>
       </c>
       <c r="D113" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E113" s="2"/>
     </row>
@@ -4518,7 +4524,7 @@
         <v>38</v>
       </c>
       <c r="D115" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E115" s="2"/>
     </row>
@@ -4608,7 +4614,7 @@
         <v>38</v>
       </c>
       <c r="D121" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E121" s="2"/>
     </row>
@@ -4623,7 +4629,7 @@
         <v>38</v>
       </c>
       <c r="D122" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E122" s="2"/>
     </row>
@@ -4668,7 +4674,7 @@
         <v>38</v>
       </c>
       <c r="D125" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E125" s="2"/>
     </row>
@@ -4683,7 +4689,7 @@
         <v>38</v>
       </c>
       <c r="D126" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E126" s="2"/>
     </row>
@@ -4698,7 +4704,7 @@
         <v>38</v>
       </c>
       <c r="D127" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E127" s="2"/>
     </row>
@@ -4713,7 +4719,7 @@
         <v>38</v>
       </c>
       <c r="D128" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E128" s="2"/>
     </row>
@@ -4743,7 +4749,7 @@
         <v>38</v>
       </c>
       <c r="D130" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E130" s="2"/>
     </row>
@@ -4758,7 +4764,7 @@
         <v>38</v>
       </c>
       <c r="D131" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E131" s="2"/>
     </row>
@@ -4773,7 +4779,7 @@
         <v>38</v>
       </c>
       <c r="D132" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E132" s="2"/>
     </row>
@@ -4788,7 +4794,7 @@
         <v>38</v>
       </c>
       <c r="D133" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E133" s="2"/>
     </row>
@@ -4893,7 +4899,7 @@
         <v>38</v>
       </c>
       <c r="D140" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E140" s="2"/>
     </row>
@@ -4923,7 +4929,7 @@
         <v>38</v>
       </c>
       <c r="D142" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E142" s="2"/>
     </row>
@@ -4983,7 +4989,7 @@
         <v>38</v>
       </c>
       <c r="D146" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E146" s="2"/>
     </row>
@@ -5028,7 +5034,7 @@
         <v>38</v>
       </c>
       <c r="D149" t="s" s="2">
-        <v>48</v>
+        <v>119</v>
       </c>
       <c r="E149" s="2"/>
     </row>
@@ -5043,7 +5049,7 @@
         <v>38</v>
       </c>
       <c r="D150" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E150" s="2"/>
     </row>
@@ -5058,7 +5064,7 @@
         <v>38</v>
       </c>
       <c r="D151" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E151" s="2"/>
     </row>
@@ -5073,7 +5079,7 @@
         <v>38</v>
       </c>
       <c r="D152" t="s" s="2">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="E152" s="2"/>
     </row>
@@ -5133,7 +5139,7 @@
         <v>38</v>
       </c>
       <c r="D156" t="s" s="2">
-        <v>39</v>
+        <v>119</v>
       </c>
       <c r="E156" s="2"/>
     </row>
@@ -5148,7 +5154,7 @@
         <v>38</v>
       </c>
       <c r="D157" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E157" s="2"/>
     </row>
@@ -5163,7 +5169,7 @@
         <v>38</v>
       </c>
       <c r="D158" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E158" s="2"/>
     </row>
@@ -5178,7 +5184,7 @@
         <v>38</v>
       </c>
       <c r="D159" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E159" s="2"/>
     </row>
@@ -5193,7 +5199,7 @@
         <v>38</v>
       </c>
       <c r="D160" t="s" s="2">
-        <v>48</v>
+        <v>119</v>
       </c>
       <c r="E160" s="2"/>
     </row>
@@ -5208,7 +5214,7 @@
         <v>38</v>
       </c>
       <c r="D161" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E161" s="2"/>
     </row>
@@ -5238,7 +5244,7 @@
         <v>38</v>
       </c>
       <c r="D163" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E163" s="2"/>
     </row>
@@ -5268,7 +5274,7 @@
         <v>38</v>
       </c>
       <c r="D165" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E165" s="2"/>
     </row>
@@ -5313,7 +5319,7 @@
         <v>38</v>
       </c>
       <c r="D168" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E168" s="2"/>
     </row>
@@ -5328,7 +5334,7 @@
         <v>38</v>
       </c>
       <c r="D169" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E169" s="2"/>
     </row>
@@ -5388,7 +5394,7 @@
         <v>38</v>
       </c>
       <c r="D173" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E173" s="2"/>
     </row>
@@ -5418,7 +5424,7 @@
         <v>38</v>
       </c>
       <c r="D175" t="s" s="2">
-        <v>39</v>
+        <v>119</v>
       </c>
       <c r="E175" s="2"/>
     </row>
@@ -5448,7 +5454,7 @@
         <v>38</v>
       </c>
       <c r="D177" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E177" s="2"/>
     </row>
@@ -5463,7 +5469,7 @@
         <v>38</v>
       </c>
       <c r="D178" t="s" s="2">
-        <v>39</v>
+        <v>119</v>
       </c>
       <c r="E178" s="2"/>
     </row>
@@ -5613,7 +5619,7 @@
         <v>38</v>
       </c>
       <c r="D188" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E188" s="2"/>
     </row>
@@ -5628,7 +5634,7 @@
         <v>38</v>
       </c>
       <c r="D189" t="s" s="2">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="E189" s="2"/>
     </row>
@@ -5643,7 +5649,7 @@
         <v>38</v>
       </c>
       <c r="D190" t="s" s="2">
-        <v>48</v>
+        <v>119</v>
       </c>
       <c r="E190" s="2"/>
     </row>
@@ -5658,7 +5664,7 @@
         <v>38</v>
       </c>
       <c r="D191" t="s" s="2">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="E191" s="2"/>
     </row>
@@ -5703,7 +5709,7 @@
         <v>38</v>
       </c>
       <c r="D194" t="s" s="2">
-        <v>39</v>
+        <v>119</v>
       </c>
       <c r="E194" s="2"/>
     </row>
@@ -5823,7 +5829,7 @@
         <v>38</v>
       </c>
       <c r="D202" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E202" s="2"/>
     </row>
@@ -5853,7 +5859,7 @@
         <v>38</v>
       </c>
       <c r="D204" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E204" s="2"/>
     </row>
@@ -5898,7 +5904,7 @@
         <v>38</v>
       </c>
       <c r="D207" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E207" s="2"/>
     </row>
@@ -5928,7 +5934,7 @@
         <v>38</v>
       </c>
       <c r="D209" t="s" s="2">
-        <v>39</v>
+        <v>119</v>
       </c>
       <c r="E209" s="2"/>
     </row>
@@ -5943,7 +5949,7 @@
         <v>38</v>
       </c>
       <c r="D210" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E210" s="2"/>
     </row>
@@ -5958,7 +5964,7 @@
         <v>38</v>
       </c>
       <c r="D211" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E211" s="2"/>
     </row>
@@ -6018,7 +6024,7 @@
         <v>38</v>
       </c>
       <c r="D215" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E215" s="2"/>
     </row>
@@ -6048,7 +6054,7 @@
         <v>38</v>
       </c>
       <c r="D217" t="s" s="2">
-        <v>39</v>
+        <v>119</v>
       </c>
       <c r="E217" s="2"/>
     </row>
@@ -6123,7 +6129,7 @@
         <v>38</v>
       </c>
       <c r="D222" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E222" s="2"/>
     </row>
@@ -6138,7 +6144,7 @@
         <v>38</v>
       </c>
       <c r="D223" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E223" s="2"/>
     </row>
@@ -6168,22 +6174,22 @@
         <v>38</v>
       </c>
       <c r="D225" t="s" s="2">
-        <v>486</v>
+        <v>39</v>
       </c>
       <c r="E225" s="2"/>
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="B226" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="B226" t="s" s="2">
+      <c r="C226" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D226" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="C226" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D226" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="E226" s="2"/>
     </row>
@@ -6228,7 +6234,7 @@
         <v>38</v>
       </c>
       <c r="D229" t="s" s="2">
-        <v>39</v>
+        <v>119</v>
       </c>
       <c r="E229" s="2"/>
     </row>
@@ -6363,22 +6369,22 @@
         <v>38</v>
       </c>
       <c r="D238" t="s" s="2">
-        <v>513</v>
+        <v>39</v>
       </c>
       <c r="E238" s="2"/>
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="B239" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="B239" t="s" s="2">
+      <c r="C239" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D239" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="C239" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D239" t="s" s="2">
-        <v>48</v>
       </c>
       <c r="E239" s="2"/>
     </row>
@@ -6393,7 +6399,7 @@
         <v>38</v>
       </c>
       <c r="D240" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E240" s="2"/>
     </row>
@@ -6453,7 +6459,7 @@
         <v>38</v>
       </c>
       <c r="D244" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E244" s="2"/>
     </row>
@@ -6513,7 +6519,7 @@
         <v>38</v>
       </c>
       <c r="D248" t="s" s="2">
-        <v>48</v>
+        <v>119</v>
       </c>
       <c r="E248" s="2"/>
     </row>
@@ -6528,7 +6534,7 @@
         <v>38</v>
       </c>
       <c r="D249" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E249" s="2"/>
     </row>
@@ -6543,7 +6549,7 @@
         <v>38</v>
       </c>
       <c r="D250" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E250" s="2"/>
     </row>
@@ -6573,7 +6579,7 @@
         <v>38</v>
       </c>
       <c r="D252" t="s" s="2">
-        <v>39</v>
+        <v>119</v>
       </c>
       <c r="E252" s="2"/>
     </row>
@@ -6588,7 +6594,7 @@
         <v>38</v>
       </c>
       <c r="D253" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E253" s="2"/>
     </row>
@@ -6603,7 +6609,7 @@
         <v>38</v>
       </c>
       <c r="D254" t="s" s="2">
-        <v>39</v>
+        <v>119</v>
       </c>
       <c r="E254" s="2"/>
     </row>
@@ -6678,7 +6684,7 @@
         <v>38</v>
       </c>
       <c r="D259" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E259" s="2"/>
     </row>
@@ -6693,7 +6699,7 @@
         <v>38</v>
       </c>
       <c r="D260" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E260" s="2"/>
     </row>
@@ -6723,7 +6729,7 @@
         <v>38</v>
       </c>
       <c r="D262" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E262" s="2"/>
     </row>
@@ -6753,7 +6759,7 @@
         <v>38</v>
       </c>
       <c r="D264" t="s" s="2">
-        <v>513</v>
+        <v>48</v>
       </c>
       <c r="E264" s="2"/>
     </row>
@@ -6768,7 +6774,7 @@
         <v>38</v>
       </c>
       <c r="D265" t="s" s="2">
-        <v>48</v>
+        <v>515</v>
       </c>
       <c r="E265" s="2"/>
     </row>
@@ -6798,7 +6804,7 @@
         <v>38</v>
       </c>
       <c r="D267" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E267" s="2"/>
     </row>
@@ -6828,7 +6834,7 @@
         <v>38</v>
       </c>
       <c r="D269" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E269" s="2"/>
     </row>
@@ -6873,7 +6879,7 @@
         <v>38</v>
       </c>
       <c r="D272" t="s" s="2">
-        <v>486</v>
+        <v>48</v>
       </c>
       <c r="E272" s="2"/>
     </row>
@@ -6888,7 +6894,7 @@
         <v>38</v>
       </c>
       <c r="D273" t="s" s="2">
-        <v>39</v>
+        <v>488</v>
       </c>
       <c r="E273" s="2"/>
     </row>
@@ -6903,7 +6909,7 @@
         <v>38</v>
       </c>
       <c r="D274" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E274" s="2"/>
     </row>
@@ -6948,7 +6954,7 @@
         <v>38</v>
       </c>
       <c r="D277" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E277" s="2"/>
     </row>
@@ -7038,7 +7044,7 @@
         <v>38</v>
       </c>
       <c r="D283" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E283" s="2"/>
     </row>
@@ -7113,7 +7119,7 @@
         <v>38</v>
       </c>
       <c r="D288" t="s" s="2">
-        <v>48</v>
+        <v>119</v>
       </c>
       <c r="E288" s="2"/>
     </row>
@@ -7128,7 +7134,7 @@
         <v>38</v>
       </c>
       <c r="D289" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E289" s="2"/>
     </row>
@@ -7158,7 +7164,7 @@
         <v>38</v>
       </c>
       <c r="D291" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E291" s="2"/>
     </row>
@@ -7173,7 +7179,7 @@
         <v>38</v>
       </c>
       <c r="D292" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E292" s="2"/>
     </row>
@@ -7263,7 +7269,7 @@
         <v>38</v>
       </c>
       <c r="D298" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E298" s="2"/>
     </row>
@@ -7293,7 +7299,7 @@
         <v>38</v>
       </c>
       <c r="D300" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E300" s="2"/>
     </row>
@@ -7353,7 +7359,7 @@
         <v>38</v>
       </c>
       <c r="D304" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E304" s="2"/>
     </row>
@@ -7368,7 +7374,7 @@
         <v>38</v>
       </c>
       <c r="D305" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E305" s="2"/>
     </row>
@@ -7443,7 +7449,7 @@
         <v>38</v>
       </c>
       <c r="D310" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E310" s="2"/>
     </row>
@@ -7458,7 +7464,7 @@
         <v>38</v>
       </c>
       <c r="D311" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E311" s="2"/>
     </row>
@@ -7518,7 +7524,7 @@
         <v>38</v>
       </c>
       <c r="D315" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E315" s="2"/>
     </row>
@@ -7548,7 +7554,7 @@
         <v>38</v>
       </c>
       <c r="D317" t="s" s="2">
-        <v>39</v>
+        <v>119</v>
       </c>
       <c r="E317" s="2"/>
     </row>
@@ -7608,7 +7614,7 @@
         <v>38</v>
       </c>
       <c r="D321" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E321" s="2"/>
     </row>
@@ -7638,7 +7644,7 @@
         <v>38</v>
       </c>
       <c r="D323" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E323" s="2"/>
     </row>
@@ -7863,7 +7869,7 @@
         <v>38</v>
       </c>
       <c r="D338" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E338" s="2"/>
     </row>
@@ -7893,7 +7899,7 @@
         <v>38</v>
       </c>
       <c r="D340" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E340" s="2"/>
     </row>
@@ -7908,7 +7914,7 @@
         <v>38</v>
       </c>
       <c r="D341" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E341" s="2"/>
     </row>
@@ -7923,7 +7929,7 @@
         <v>38</v>
       </c>
       <c r="D342" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E342" s="2"/>
     </row>
@@ -7938,7 +7944,7 @@
         <v>38</v>
       </c>
       <c r="D343" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E343" s="2"/>
     </row>
@@ -7968,7 +7974,7 @@
         <v>38</v>
       </c>
       <c r="D345" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E345" s="2"/>
     </row>
@@ -7998,7 +8004,7 @@
         <v>38</v>
       </c>
       <c r="D347" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E347" s="2"/>
     </row>
@@ -8058,7 +8064,7 @@
         <v>38</v>
       </c>
       <c r="D351" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E351" s="2"/>
     </row>
@@ -8118,7 +8124,7 @@
         <v>38</v>
       </c>
       <c r="D355" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E355" s="2"/>
     </row>
@@ -8163,7 +8169,7 @@
         <v>38</v>
       </c>
       <c r="D358" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E358" s="2"/>
     </row>
@@ -8283,7 +8289,7 @@
         <v>38</v>
       </c>
       <c r="D366" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E366" s="2"/>
     </row>
@@ -8313,7 +8319,7 @@
         <v>38</v>
       </c>
       <c r="D368" t="s" s="2">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="E368" s="2"/>
     </row>
@@ -8328,7 +8334,7 @@
         <v>38</v>
       </c>
       <c r="D369" t="s" s="2">
-        <v>39</v>
+        <v>119</v>
       </c>
       <c r="E369" s="2"/>
     </row>
@@ -8403,7 +8409,7 @@
         <v>38</v>
       </c>
       <c r="D374" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E374" s="2"/>
     </row>
@@ -8418,7 +8424,7 @@
         <v>38</v>
       </c>
       <c r="D375" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E375" s="2"/>
     </row>
@@ -8433,7 +8439,7 @@
         <v>38</v>
       </c>
       <c r="D376" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E376" s="2"/>
     </row>
@@ -8448,7 +8454,7 @@
         <v>38</v>
       </c>
       <c r="D377" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E377" s="2"/>
     </row>
@@ -8463,7 +8469,7 @@
         <v>38</v>
       </c>
       <c r="D378" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E378" s="2"/>
     </row>
@@ -8478,7 +8484,7 @@
         <v>38</v>
       </c>
       <c r="D379" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E379" s="2"/>
     </row>
@@ -8493,7 +8499,7 @@
         <v>38</v>
       </c>
       <c r="D380" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E380" s="2"/>
     </row>
@@ -8508,7 +8514,7 @@
         <v>38</v>
       </c>
       <c r="D381" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E381" s="2"/>
     </row>
@@ -8523,9 +8529,24 @@
         <v>38</v>
       </c>
       <c r="D382" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E382" s="2"/>
+    </row>
+    <row r="383">
+      <c r="A383" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="B383" t="s" s="2">
+        <v>803</v>
+      </c>
+      <c r="C383" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D383" t="s" s="2">
         <v>48</v>
       </c>
-      <c r="E382" s="2"/>
+      <c r="E383" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -8556,7 +8577,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>34</v>
@@ -8573,40 +8594,40 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="C3" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="C4" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C5" t="s" s="2">
         <v>38</v>
@@ -8618,10 +8639,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="C6" t="s" s="2">
         <v>38</v>
@@ -8633,16 +8654,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="C7" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E7" s="2"/>
     </row>
@@ -8675,7 +8696,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>34</v>
@@ -8692,10 +8713,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="C3" t="s" s="2">
         <v>38</v>
@@ -8707,10 +8728,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C4" t="s" s="2">
         <v>38</v>
@@ -8722,10 +8743,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C5" t="s" s="2">
         <v>38</v>
@@ -8737,10 +8758,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C6" t="s" s="2">
         <v>38</v>
@@ -8752,10 +8773,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C7" t="s" s="2">
         <v>38</v>
@@ -8767,10 +8788,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="C8" t="s" s="2">
         <v>38</v>
@@ -8782,10 +8803,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C9" t="s" s="2">
         <v>38</v>
@@ -8797,10 +8818,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="C10" t="s" s="2">
         <v>38</v>
@@ -8812,10 +8833,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="C11" t="s" s="2">
         <v>38</v>
@@ -8827,10 +8848,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="C12" t="s" s="2">
         <v>38</v>

--- a/ig/ch-elm/ch-elm-results-to-foph-patient-name-representation.xlsx
+++ b/ig/ch-elm/ch-elm-results-to-foph-patient-name-representation.xlsx
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.0</t>
+    <t>1.14.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T14:58:40+00:00</t>
+    <t>2026-07-01T19:23:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1265,6 +1265,12 @@
     <t>Neisseria gonorrhoeae rRNA [Presence] in Vaginal fluid by NAA with probe detection</t>
   </si>
   <si>
+    <t>539-7</t>
+  </si>
+  <si>
+    <t>Mycobacterium sp identified in Sputum by Organism specific culture</t>
+  </si>
+  <si>
     <t>53917-1</t>
   </si>
   <si>
@@ -1305,12 +1311,6 @@
   </si>
   <si>
     <t>Escherichia coli shiga-like toxin identified in Specimen</t>
-  </si>
-  <si>
-    <t>539-7</t>
-  </si>
-  <si>
-    <t>Mycobacterium sp identified in Sputum by Organism specific culture</t>
   </si>
   <si>
     <t>540-5</t>
@@ -5664,7 +5664,7 @@
         <v>38</v>
       </c>
       <c r="D191" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E191" s="2"/>
     </row>
@@ -5679,7 +5679,7 @@
         <v>38</v>
       </c>
       <c r="D192" t="s" s="2">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="E192" s="2"/>
     </row>
@@ -5724,7 +5724,7 @@
         <v>38</v>
       </c>
       <c r="D195" t="s" s="2">
-        <v>39</v>
+        <v>119</v>
       </c>
       <c r="E195" s="2"/>
     </row>

--- a/ig/ch-elm/ch-elm-results-to-foph-patient-name-representation.xlsx
+++ b/ig/ch-elm/ch-elm-results-to-foph-patient-name-representation.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1645" uniqueCount="836">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1689" uniqueCount="858">
   <si>
     <t>Property</t>
   </si>
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.1</t>
+    <t>1.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T19:23:08+00:00</t>
+    <t>2026-08-12T07:20:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -182,6 +182,12 @@
     <t>Legionella sp DNA [Presence] in Specimen by NAA with probe detection</t>
   </si>
   <si>
+    <t>101298-8</t>
+  </si>
+  <si>
+    <t>Respiratory syncytial virus RNA [Presence] in Throat by NAA with non-probe detection</t>
+  </si>
+  <si>
     <t>101307-7</t>
   </si>
   <si>
@@ -308,6 +314,18 @@
     <t>Shigella species+EIEC invasion plasmid antigen H ipaH gene [Presence] in Specimen</t>
   </si>
   <si>
+    <t>105211-7</t>
+  </si>
+  <si>
+    <t>Respiratory syncytial virus RNA [Presence] in Bronchial specimen by NAA with probe detection</t>
+  </si>
+  <si>
+    <t>105231-5</t>
+  </si>
+  <si>
+    <t>Respiratory syncytial virus RNA [Presence] in Sputum by NAA with probe detection</t>
+  </si>
+  <si>
     <t>105640-7</t>
   </si>
   <si>
@@ -326,6 +344,18 @@
     <t>Tick-borne encephalitis virus Ab [Interpretation] in Serum or Plasma</t>
   </si>
   <si>
+    <t>108111-6</t>
+  </si>
+  <si>
+    <t>Hantavirus RNA [Presence] in Specimen by NAA with probe detection</t>
+  </si>
+  <si>
+    <t>111556-7</t>
+  </si>
+  <si>
+    <t>Respiratory syncytial virus RNA [Presence] in Bronchoalveolar aspirate by NAA with non-probe detection</t>
+  </si>
+  <si>
     <t>11259-9</t>
   </si>
   <si>
@@ -923,6 +953,12 @@
     <t>Influenza virus B RNA [Presence] in Specimen by NAA with probe detection</t>
   </si>
   <si>
+    <t>40988-8</t>
+  </si>
+  <si>
+    <t>Respiratory syncytial virus RNA [Presence] in Specimen by NAA with probe detection</t>
+  </si>
+  <si>
     <t>41216-3</t>
   </si>
   <si>
@@ -1733,6 +1769,18 @@
     <t>Influenza virus B RNA [Presence] in Nasopharynx by NAA with probe detection</t>
   </si>
   <si>
+    <t>76088-4</t>
+  </si>
+  <si>
+    <t>Respiratory syncytial virus RNA [Presence] in Bronchoalveolar lavage by NAA with probe detection</t>
+  </si>
+  <si>
+    <t>76089-2</t>
+  </si>
+  <si>
+    <t>Respiratory syncytial virus RNA [Presence] in Nasopharynx by NAA with probe detection</t>
+  </si>
+  <si>
     <t>76626-1</t>
   </si>
   <si>
@@ -1931,6 +1979,12 @@
     <t>Influenza virus B RNA [Presence] in Upper respiratory specimen by NAA with probe detection</t>
   </si>
   <si>
+    <t>85479-4</t>
+  </si>
+  <si>
+    <t>Respiratory syncytial virus RNA [Presence] in Upper respiratory specimen by NAA with probe detection</t>
+  </si>
+  <si>
     <t>85622-9</t>
   </si>
   <si>
@@ -2123,6 +2177,12 @@
     <t>Measles virus RNA [Presence] in Lower respiratory specimen by NAA with probe detection</t>
   </si>
   <si>
+    <t>91133-9</t>
+  </si>
+  <si>
+    <t>Respiratory syncytial virus RNA [Presence] in Lower respiratory specimen by NAA with probe detection</t>
+  </si>
+  <si>
     <t>91780-7</t>
   </si>
   <si>
@@ -2157,6 +2217,12 @@
   </si>
   <si>
     <t>Middle East respiratory syndrome coronavirus (MERS-CoV) RNA [Presence] in Lower respiratory specimen by NAA with probe detection</t>
+  </si>
+  <si>
+    <t>92131-2</t>
+  </si>
+  <si>
+    <t>Respiratory syncytial virus RNA [Presence] in Respiratory system specimen by NAA with probe detection</t>
   </si>
   <si>
     <t>92141-1</t>
@@ -2796,7 +2862,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E383"/>
+  <dimension ref="A1:E394"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2964,7 +3030,7 @@
         <v>38</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E11" s="2"/>
     </row>
@@ -2979,7 +3045,7 @@
         <v>38</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E12" s="2"/>
     </row>
@@ -3039,7 +3105,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E16" s="2"/>
     </row>
@@ -3054,7 +3120,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E17" s="2"/>
     </row>
@@ -3084,7 +3150,7 @@
         <v>38</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E19" s="2"/>
     </row>
@@ -3204,7 +3270,7 @@
         <v>38</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E27" s="2"/>
     </row>
@@ -3249,7 +3315,7 @@
         <v>38</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E30" s="2"/>
     </row>
@@ -3279,7 +3345,7 @@
         <v>38</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E32" s="2"/>
     </row>
@@ -3294,7 +3360,7 @@
         <v>38</v>
       </c>
       <c r="D33" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E33" s="2"/>
     </row>
@@ -3324,7 +3390,7 @@
         <v>38</v>
       </c>
       <c r="D35" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E35" s="2"/>
     </row>
@@ -3354,7 +3420,7 @@
         <v>38</v>
       </c>
       <c r="D37" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E37" s="2"/>
     </row>
@@ -3369,7 +3435,7 @@
         <v>38</v>
       </c>
       <c r="D38" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E38" s="2"/>
     </row>
@@ -3384,7 +3450,7 @@
         <v>38</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E39" s="2"/>
     </row>
@@ -3429,16 +3495,16 @@
         <v>38</v>
       </c>
       <c r="D42" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E42" s="2"/>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="B43" t="s" s="2">
         <v>120</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>121</v>
       </c>
       <c r="C43" t="s" s="2">
         <v>38</v>
@@ -3450,61 +3516,61 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="B44" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="B44" t="s" s="2">
-        <v>123</v>
-      </c>
       <c r="C44" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D44" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E44" s="2"/>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="B45" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="B45" t="s" s="2">
-        <v>125</v>
-      </c>
       <c r="C45" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D45" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E45" s="2"/>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="B46" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="B46" t="s" s="2">
-        <v>127</v>
-      </c>
       <c r="C46" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D46" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E46" s="2"/>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="B47" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="B47" t="s" s="2">
+      <c r="C47" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D47" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="C47" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D47" t="s" s="2">
-        <v>39</v>
       </c>
       <c r="E47" s="2"/>
     </row>
@@ -3519,7 +3585,7 @@
         <v>38</v>
       </c>
       <c r="D48" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E48" s="2"/>
     </row>
@@ -3534,7 +3600,7 @@
         <v>38</v>
       </c>
       <c r="D49" t="s" s="2">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E49" s="2"/>
     </row>
@@ -3549,7 +3615,7 @@
         <v>38</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E50" s="2"/>
     </row>
@@ -3564,7 +3630,7 @@
         <v>38</v>
       </c>
       <c r="D51" t="s" s="2">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E51" s="2"/>
     </row>
@@ -3594,7 +3660,7 @@
         <v>38</v>
       </c>
       <c r="D53" t="s" s="2">
-        <v>48</v>
+        <v>129</v>
       </c>
       <c r="E53" s="2"/>
     </row>
@@ -3624,7 +3690,7 @@
         <v>38</v>
       </c>
       <c r="D55" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E55" s="2"/>
     </row>
@@ -3639,7 +3705,7 @@
         <v>38</v>
       </c>
       <c r="D56" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E56" s="2"/>
     </row>
@@ -3654,7 +3720,7 @@
         <v>38</v>
       </c>
       <c r="D57" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E57" s="2"/>
     </row>
@@ -3669,7 +3735,7 @@
         <v>38</v>
       </c>
       <c r="D58" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E58" s="2"/>
     </row>
@@ -3699,7 +3765,7 @@
         <v>38</v>
       </c>
       <c r="D60" t="s" s="2">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="E60" s="2"/>
     </row>
@@ -3714,7 +3780,7 @@
         <v>38</v>
       </c>
       <c r="D61" t="s" s="2">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="E61" s="2"/>
     </row>
@@ -3729,7 +3795,7 @@
         <v>38</v>
       </c>
       <c r="D62" t="s" s="2">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E62" s="2"/>
     </row>
@@ -3744,7 +3810,7 @@
         <v>38</v>
       </c>
       <c r="D63" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E63" s="2"/>
     </row>
@@ -3774,7 +3840,7 @@
         <v>38</v>
       </c>
       <c r="D65" t="s" s="2">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E65" s="2"/>
     </row>
@@ -3789,7 +3855,7 @@
         <v>38</v>
       </c>
       <c r="D66" t="s" s="2">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E66" s="2"/>
     </row>
@@ -3819,7 +3885,7 @@
         <v>38</v>
       </c>
       <c r="D68" t="s" s="2">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E68" s="2"/>
     </row>
@@ -3849,7 +3915,7 @@
         <v>38</v>
       </c>
       <c r="D70" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E70" s="2"/>
     </row>
@@ -3864,7 +3930,7 @@
         <v>38</v>
       </c>
       <c r="D71" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E71" s="2"/>
     </row>
@@ -3879,7 +3945,7 @@
         <v>38</v>
       </c>
       <c r="D72" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E72" s="2"/>
     </row>
@@ -3894,7 +3960,7 @@
         <v>38</v>
       </c>
       <c r="D73" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E73" s="2"/>
     </row>
@@ -3924,7 +3990,7 @@
         <v>38</v>
       </c>
       <c r="D75" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E75" s="2"/>
     </row>
@@ -3939,7 +4005,7 @@
         <v>38</v>
       </c>
       <c r="D76" t="s" s="2">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="E76" s="2"/>
     </row>
@@ -3954,7 +4020,7 @@
         <v>38</v>
       </c>
       <c r="D77" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E77" s="2"/>
     </row>
@@ -3969,7 +4035,7 @@
         <v>38</v>
       </c>
       <c r="D78" t="s" s="2">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E78" s="2"/>
     </row>
@@ -3984,7 +4050,7 @@
         <v>38</v>
       </c>
       <c r="D79" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E79" s="2"/>
     </row>
@@ -3999,7 +4065,7 @@
         <v>38</v>
       </c>
       <c r="D80" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E80" s="2"/>
     </row>
@@ -4014,7 +4080,7 @@
         <v>38</v>
       </c>
       <c r="D81" t="s" s="2">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E81" s="2"/>
     </row>
@@ -4029,7 +4095,7 @@
         <v>38</v>
       </c>
       <c r="D82" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E82" s="2"/>
     </row>
@@ -4059,7 +4125,7 @@
         <v>38</v>
       </c>
       <c r="D84" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E84" s="2"/>
     </row>
@@ -4104,7 +4170,7 @@
         <v>38</v>
       </c>
       <c r="D87" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E87" s="2"/>
     </row>
@@ -4149,7 +4215,7 @@
         <v>38</v>
       </c>
       <c r="D90" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E90" s="2"/>
     </row>
@@ -4179,7 +4245,7 @@
         <v>38</v>
       </c>
       <c r="D92" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E92" s="2"/>
     </row>
@@ -4224,7 +4290,7 @@
         <v>38</v>
       </c>
       <c r="D95" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E95" s="2"/>
     </row>
@@ -4239,7 +4305,7 @@
         <v>38</v>
       </c>
       <c r="D96" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E96" s="2"/>
     </row>
@@ -4254,7 +4320,7 @@
         <v>38</v>
       </c>
       <c r="D97" t="s" s="2">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E97" s="2"/>
     </row>
@@ -4269,7 +4335,7 @@
         <v>38</v>
       </c>
       <c r="D98" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E98" s="2"/>
     </row>
@@ -4284,7 +4350,7 @@
         <v>38</v>
       </c>
       <c r="D99" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E99" s="2"/>
     </row>
@@ -4299,7 +4365,7 @@
         <v>38</v>
       </c>
       <c r="D100" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E100" s="2"/>
     </row>
@@ -4314,7 +4380,7 @@
         <v>38</v>
       </c>
       <c r="D101" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E101" s="2"/>
     </row>
@@ -4344,7 +4410,7 @@
         <v>38</v>
       </c>
       <c r="D103" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E103" s="2"/>
     </row>
@@ -4359,7 +4425,7 @@
         <v>38</v>
       </c>
       <c r="D104" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E104" s="2"/>
     </row>
@@ -4419,7 +4485,7 @@
         <v>38</v>
       </c>
       <c r="D108" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E108" s="2"/>
     </row>
@@ -4449,7 +4515,7 @@
         <v>38</v>
       </c>
       <c r="D110" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E110" s="2"/>
     </row>
@@ -4479,7 +4545,7 @@
         <v>38</v>
       </c>
       <c r="D112" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E112" s="2"/>
     </row>
@@ -4494,7 +4560,7 @@
         <v>38</v>
       </c>
       <c r="D113" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E113" s="2"/>
     </row>
@@ -4509,7 +4575,7 @@
         <v>38</v>
       </c>
       <c r="D114" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E114" s="2"/>
     </row>
@@ -4554,7 +4620,7 @@
         <v>38</v>
       </c>
       <c r="D117" t="s" s="2">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E117" s="2"/>
     </row>
@@ -4584,7 +4650,7 @@
         <v>38</v>
       </c>
       <c r="D119" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E119" s="2"/>
     </row>
@@ -4599,7 +4665,7 @@
         <v>38</v>
       </c>
       <c r="D120" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E120" s="2"/>
     </row>
@@ -4629,7 +4695,7 @@
         <v>38</v>
       </c>
       <c r="D122" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E122" s="2"/>
     </row>
@@ -4689,7 +4755,7 @@
         <v>38</v>
       </c>
       <c r="D126" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E126" s="2"/>
     </row>
@@ -4704,7 +4770,7 @@
         <v>38</v>
       </c>
       <c r="D127" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E127" s="2"/>
     </row>
@@ -4719,7 +4785,7 @@
         <v>38</v>
       </c>
       <c r="D128" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E128" s="2"/>
     </row>
@@ -4839,7 +4905,7 @@
         <v>38</v>
       </c>
       <c r="D136" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E136" s="2"/>
     </row>
@@ -4869,7 +4935,7 @@
         <v>38</v>
       </c>
       <c r="D138" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E138" s="2"/>
     </row>
@@ -4884,7 +4950,7 @@
         <v>38</v>
       </c>
       <c r="D139" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E139" s="2"/>
     </row>
@@ -4914,7 +4980,7 @@
         <v>38</v>
       </c>
       <c r="D141" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E141" s="2"/>
     </row>
@@ -4929,7 +4995,7 @@
         <v>38</v>
       </c>
       <c r="D142" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E142" s="2"/>
     </row>
@@ -5004,7 +5070,7 @@
         <v>38</v>
       </c>
       <c r="D147" t="s" s="2">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="E147" s="2"/>
     </row>
@@ -5019,7 +5085,7 @@
         <v>38</v>
       </c>
       <c r="D148" t="s" s="2">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="E148" s="2"/>
     </row>
@@ -5034,7 +5100,7 @@
         <v>38</v>
       </c>
       <c r="D149" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E149" s="2"/>
     </row>
@@ -5049,7 +5115,7 @@
         <v>38</v>
       </c>
       <c r="D150" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E150" s="2"/>
     </row>
@@ -5079,7 +5145,7 @@
         <v>38</v>
       </c>
       <c r="D152" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E152" s="2"/>
     </row>
@@ -5094,7 +5160,7 @@
         <v>38</v>
       </c>
       <c r="D153" t="s" s="2">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="E153" s="2"/>
     </row>
@@ -5109,7 +5175,7 @@
         <v>38</v>
       </c>
       <c r="D154" t="s" s="2">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="E154" s="2"/>
     </row>
@@ -5124,7 +5190,7 @@
         <v>38</v>
       </c>
       <c r="D155" t="s" s="2">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="E155" s="2"/>
     </row>
@@ -5139,7 +5205,7 @@
         <v>38</v>
       </c>
       <c r="D156" t="s" s="2">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="E156" s="2"/>
     </row>
@@ -5184,7 +5250,7 @@
         <v>38</v>
       </c>
       <c r="D159" t="s" s="2">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E159" s="2"/>
     </row>
@@ -5199,7 +5265,7 @@
         <v>38</v>
       </c>
       <c r="D160" t="s" s="2">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="E160" s="2"/>
     </row>
@@ -5214,7 +5280,7 @@
         <v>38</v>
       </c>
       <c r="D161" t="s" s="2">
-        <v>48</v>
+        <v>129</v>
       </c>
       <c r="E161" s="2"/>
     </row>
@@ -5229,7 +5295,7 @@
         <v>38</v>
       </c>
       <c r="D162" t="s" s="2">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E162" s="2"/>
     </row>
@@ -5274,7 +5340,7 @@
         <v>38</v>
       </c>
       <c r="D165" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E165" s="2"/>
     </row>
@@ -5289,7 +5355,7 @@
         <v>38</v>
       </c>
       <c r="D166" t="s" s="2">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E166" s="2"/>
     </row>
@@ -5304,7 +5370,7 @@
         <v>38</v>
       </c>
       <c r="D167" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E167" s="2"/>
     </row>
@@ -5334,7 +5400,7 @@
         <v>38</v>
       </c>
       <c r="D169" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E169" s="2"/>
     </row>
@@ -5349,7 +5415,7 @@
         <v>38</v>
       </c>
       <c r="D170" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E170" s="2"/>
     </row>
@@ -5364,7 +5430,7 @@
         <v>38</v>
       </c>
       <c r="D171" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E171" s="2"/>
     </row>
@@ -5409,7 +5475,7 @@
         <v>38</v>
       </c>
       <c r="D174" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E174" s="2"/>
     </row>
@@ -5424,7 +5490,7 @@
         <v>38</v>
       </c>
       <c r="D175" t="s" s="2">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="E175" s="2"/>
     </row>
@@ -5469,7 +5535,7 @@
         <v>38</v>
       </c>
       <c r="D178" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E178" s="2"/>
     </row>
@@ -5499,7 +5565,7 @@
         <v>38</v>
       </c>
       <c r="D180" t="s" s="2">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E180" s="2"/>
     </row>
@@ -5514,7 +5580,7 @@
         <v>38</v>
       </c>
       <c r="D181" t="s" s="2">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E181" s="2"/>
     </row>
@@ -5559,7 +5625,7 @@
         <v>38</v>
       </c>
       <c r="D184" t="s" s="2">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E184" s="2"/>
     </row>
@@ -5634,7 +5700,7 @@
         <v>38</v>
       </c>
       <c r="D189" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E189" s="2"/>
     </row>
@@ -5649,7 +5715,7 @@
         <v>38</v>
       </c>
       <c r="D190" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E190" s="2"/>
     </row>
@@ -5679,7 +5745,7 @@
         <v>38</v>
       </c>
       <c r="D192" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E192" s="2"/>
     </row>
@@ -5694,7 +5760,7 @@
         <v>38</v>
       </c>
       <c r="D193" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E193" s="2"/>
     </row>
@@ -5709,7 +5775,7 @@
         <v>38</v>
       </c>
       <c r="D194" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E194" s="2"/>
     </row>
@@ -5724,7 +5790,7 @@
         <v>38</v>
       </c>
       <c r="D195" t="s" s="2">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="E195" s="2"/>
     </row>
@@ -5739,7 +5805,7 @@
         <v>38</v>
       </c>
       <c r="D196" t="s" s="2">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E196" s="2"/>
     </row>
@@ -5769,7 +5835,7 @@
         <v>38</v>
       </c>
       <c r="D198" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E198" s="2"/>
     </row>
@@ -5784,7 +5850,7 @@
         <v>38</v>
       </c>
       <c r="D199" t="s" s="2">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E199" s="2"/>
     </row>
@@ -5799,7 +5865,7 @@
         <v>38</v>
       </c>
       <c r="D200" t="s" s="2">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E200" s="2"/>
     </row>
@@ -5814,7 +5880,7 @@
         <v>38</v>
       </c>
       <c r="D201" t="s" s="2">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E201" s="2"/>
     </row>
@@ -5844,7 +5910,7 @@
         <v>38</v>
       </c>
       <c r="D203" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E203" s="2"/>
     </row>
@@ -5859,7 +5925,7 @@
         <v>38</v>
       </c>
       <c r="D204" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E204" s="2"/>
     </row>
@@ -5919,7 +5985,7 @@
         <v>38</v>
       </c>
       <c r="D208" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E208" s="2"/>
     </row>
@@ -5934,7 +6000,7 @@
         <v>38</v>
       </c>
       <c r="D209" t="s" s="2">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="E209" s="2"/>
     </row>
@@ -5949,7 +6015,7 @@
         <v>38</v>
       </c>
       <c r="D210" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E210" s="2"/>
     </row>
@@ -5964,7 +6030,7 @@
         <v>38</v>
       </c>
       <c r="D211" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E211" s="2"/>
     </row>
@@ -6009,7 +6075,7 @@
         <v>38</v>
       </c>
       <c r="D214" t="s" s="2">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E214" s="2"/>
     </row>
@@ -6024,7 +6090,7 @@
         <v>38</v>
       </c>
       <c r="D215" t="s" s="2">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E215" s="2"/>
     </row>
@@ -6039,7 +6105,7 @@
         <v>38</v>
       </c>
       <c r="D216" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E216" s="2"/>
     </row>
@@ -6054,7 +6120,7 @@
         <v>38</v>
       </c>
       <c r="D217" t="s" s="2">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="E217" s="2"/>
     </row>
@@ -6129,7 +6195,7 @@
         <v>38</v>
       </c>
       <c r="D222" t="s" s="2">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E222" s="2"/>
     </row>
@@ -6144,7 +6210,7 @@
         <v>38</v>
       </c>
       <c r="D223" t="s" s="2">
-        <v>48</v>
+        <v>129</v>
       </c>
       <c r="E223" s="2"/>
     </row>
@@ -6189,61 +6255,61 @@
         <v>38</v>
       </c>
       <c r="D226" t="s" s="2">
-        <v>488</v>
+        <v>39</v>
       </c>
       <c r="E226" s="2"/>
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="B227" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="B227" t="s" s="2">
-        <v>490</v>
-      </c>
       <c r="C227" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D227" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E227" s="2"/>
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="B228" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="B228" t="s" s="2">
-        <v>492</v>
-      </c>
       <c r="C228" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D228" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E228" s="2"/>
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="B229" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="B229" t="s" s="2">
-        <v>494</v>
-      </c>
       <c r="C229" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D229" t="s" s="2">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="E229" s="2"/>
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="B230" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="B230" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="C230" t="s" s="2">
         <v>38</v>
@@ -6255,10 +6321,10 @@
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="B231" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="B231" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="C231" t="s" s="2">
         <v>38</v>
@@ -6270,16 +6336,16 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="B232" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="B232" t="s" s="2">
+      <c r="C232" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D232" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="C232" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D232" t="s" s="2">
-        <v>39</v>
       </c>
       <c r="E232" s="2"/>
     </row>
@@ -6294,7 +6360,7 @@
         <v>38</v>
       </c>
       <c r="D233" t="s" s="2">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E233" s="2"/>
     </row>
@@ -6309,7 +6375,7 @@
         <v>38</v>
       </c>
       <c r="D234" t="s" s="2">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E234" s="2"/>
     </row>
@@ -6324,7 +6390,7 @@
         <v>38</v>
       </c>
       <c r="D235" t="s" s="2">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E235" s="2"/>
     </row>
@@ -6384,31 +6450,31 @@
         <v>38</v>
       </c>
       <c r="D239" t="s" s="2">
-        <v>515</v>
+        <v>39</v>
       </c>
       <c r="E239" s="2"/>
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="B240" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="B240" t="s" s="2">
-        <v>517</v>
-      </c>
       <c r="C240" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D240" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E240" s="2"/>
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="B241" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="B241" t="s" s="2">
-        <v>519</v>
       </c>
       <c r="C241" t="s" s="2">
         <v>38</v>
@@ -6420,10 +6486,10 @@
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="B242" t="s" s="2">
         <v>520</v>
-      </c>
-      <c r="B242" t="s" s="2">
-        <v>521</v>
       </c>
       <c r="C242" t="s" s="2">
         <v>38</v>
@@ -6435,10 +6501,10 @@
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="B243" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="B243" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="C243" t="s" s="2">
         <v>38</v>
@@ -6450,10 +6516,10 @@
     </row>
     <row r="244">
       <c r="A244" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="B244" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="B244" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="C244" t="s" s="2">
         <v>38</v>
@@ -6465,16 +6531,16 @@
     </row>
     <row r="245">
       <c r="A245" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="B245" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="B245" t="s" s="2">
+      <c r="C245" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D245" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="C245" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D245" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="E245" s="2"/>
     </row>
@@ -6489,7 +6555,7 @@
         <v>38</v>
       </c>
       <c r="D246" t="s" s="2">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="E246" s="2"/>
     </row>
@@ -6504,7 +6570,7 @@
         <v>38</v>
       </c>
       <c r="D247" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E247" s="2"/>
     </row>
@@ -6519,7 +6585,7 @@
         <v>38</v>
       </c>
       <c r="D248" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E248" s="2"/>
     </row>
@@ -6534,7 +6600,7 @@
         <v>38</v>
       </c>
       <c r="D249" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E249" s="2"/>
     </row>
@@ -6564,7 +6630,7 @@
         <v>38</v>
       </c>
       <c r="D251" t="s" s="2">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="E251" s="2"/>
     </row>
@@ -6579,7 +6645,7 @@
         <v>38</v>
       </c>
       <c r="D252" t="s" s="2">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="E252" s="2"/>
     </row>
@@ -6594,7 +6660,7 @@
         <v>38</v>
       </c>
       <c r="D253" t="s" s="2">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E253" s="2"/>
     </row>
@@ -6609,7 +6675,7 @@
         <v>38</v>
       </c>
       <c r="D254" t="s" s="2">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="E254" s="2"/>
     </row>
@@ -6624,7 +6690,7 @@
         <v>38</v>
       </c>
       <c r="D255" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E255" s="2"/>
     </row>
@@ -6654,7 +6720,7 @@
         <v>38</v>
       </c>
       <c r="D257" t="s" s="2">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E257" s="2"/>
     </row>
@@ -6669,7 +6735,7 @@
         <v>38</v>
       </c>
       <c r="D258" t="s" s="2">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E258" s="2"/>
     </row>
@@ -6699,7 +6765,7 @@
         <v>38</v>
       </c>
       <c r="D260" t="s" s="2">
-        <v>48</v>
+        <v>129</v>
       </c>
       <c r="E260" s="2"/>
     </row>
@@ -6744,7 +6810,7 @@
         <v>38</v>
       </c>
       <c r="D263" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E263" s="2"/>
     </row>
@@ -6759,7 +6825,7 @@
         <v>38</v>
       </c>
       <c r="D264" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E264" s="2"/>
     </row>
@@ -6774,7 +6840,7 @@
         <v>38</v>
       </c>
       <c r="D265" t="s" s="2">
-        <v>515</v>
+        <v>39</v>
       </c>
       <c r="E265" s="2"/>
     </row>
@@ -6804,7 +6870,7 @@
         <v>38</v>
       </c>
       <c r="D267" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E267" s="2"/>
     </row>
@@ -6834,7 +6900,7 @@
         <v>38</v>
       </c>
       <c r="D269" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E269" s="2"/>
     </row>
@@ -6864,7 +6930,7 @@
         <v>38</v>
       </c>
       <c r="D271" t="s" s="2">
-        <v>48</v>
+        <v>527</v>
       </c>
       <c r="E271" s="2"/>
     </row>
@@ -6894,7 +6960,7 @@
         <v>38</v>
       </c>
       <c r="D273" t="s" s="2">
-        <v>488</v>
+        <v>48</v>
       </c>
       <c r="E273" s="2"/>
     </row>
@@ -6909,7 +6975,7 @@
         <v>38</v>
       </c>
       <c r="D274" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E274" s="2"/>
     </row>
@@ -6939,7 +7005,7 @@
         <v>38</v>
       </c>
       <c r="D276" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E276" s="2"/>
     </row>
@@ -6954,7 +7020,7 @@
         <v>38</v>
       </c>
       <c r="D277" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E277" s="2"/>
     </row>
@@ -6969,7 +7035,7 @@
         <v>38</v>
       </c>
       <c r="D278" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E278" s="2"/>
     </row>
@@ -6984,7 +7050,7 @@
         <v>38</v>
       </c>
       <c r="D279" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E279" s="2"/>
     </row>
@@ -6999,7 +7065,7 @@
         <v>38</v>
       </c>
       <c r="D280" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E280" s="2"/>
     </row>
@@ -7014,7 +7080,7 @@
         <v>38</v>
       </c>
       <c r="D281" t="s" s="2">
-        <v>39</v>
+        <v>500</v>
       </c>
       <c r="E281" s="2"/>
     </row>
@@ -7044,7 +7110,7 @@
         <v>38</v>
       </c>
       <c r="D283" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E283" s="2"/>
     </row>
@@ -7059,7 +7125,7 @@
         <v>38</v>
       </c>
       <c r="D284" t="s" s="2">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="E284" s="2"/>
     </row>
@@ -7074,7 +7140,7 @@
         <v>38</v>
       </c>
       <c r="D285" t="s" s="2">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="E285" s="2"/>
     </row>
@@ -7089,7 +7155,7 @@
         <v>38</v>
       </c>
       <c r="D286" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E286" s="2"/>
     </row>
@@ -7104,7 +7170,7 @@
         <v>38</v>
       </c>
       <c r="D287" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E287" s="2"/>
     </row>
@@ -7119,7 +7185,7 @@
         <v>38</v>
       </c>
       <c r="D288" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E288" s="2"/>
     </row>
@@ -7134,7 +7200,7 @@
         <v>38</v>
       </c>
       <c r="D289" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E289" s="2"/>
     </row>
@@ -7179,7 +7245,7 @@
         <v>38</v>
       </c>
       <c r="D292" t="s" s="2">
-        <v>48</v>
+        <v>129</v>
       </c>
       <c r="E292" s="2"/>
     </row>
@@ -7194,7 +7260,7 @@
         <v>38</v>
       </c>
       <c r="D293" t="s" s="2">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E293" s="2"/>
     </row>
@@ -7209,7 +7275,7 @@
         <v>38</v>
       </c>
       <c r="D294" t="s" s="2">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E294" s="2"/>
     </row>
@@ -7224,7 +7290,7 @@
         <v>38</v>
       </c>
       <c r="D295" t="s" s="2">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E295" s="2"/>
     </row>
@@ -7239,7 +7305,7 @@
         <v>38</v>
       </c>
       <c r="D296" t="s" s="2">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E296" s="2"/>
     </row>
@@ -7254,7 +7320,7 @@
         <v>38</v>
       </c>
       <c r="D297" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E297" s="2"/>
     </row>
@@ -7284,7 +7350,7 @@
         <v>38</v>
       </c>
       <c r="D299" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E299" s="2"/>
     </row>
@@ -7374,7 +7440,7 @@
         <v>38</v>
       </c>
       <c r="D305" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E305" s="2"/>
     </row>
@@ -7404,7 +7470,7 @@
         <v>38</v>
       </c>
       <c r="D307" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E307" s="2"/>
     </row>
@@ -7419,7 +7485,7 @@
         <v>38</v>
       </c>
       <c r="D308" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E308" s="2"/>
     </row>
@@ -7434,7 +7500,7 @@
         <v>38</v>
       </c>
       <c r="D309" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E309" s="2"/>
     </row>
@@ -7464,7 +7530,7 @@
         <v>38</v>
       </c>
       <c r="D311" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E311" s="2"/>
     </row>
@@ -7509,7 +7575,7 @@
         <v>38</v>
       </c>
       <c r="D314" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E314" s="2"/>
     </row>
@@ -7539,7 +7605,7 @@
         <v>38</v>
       </c>
       <c r="D316" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E316" s="2"/>
     </row>
@@ -7554,7 +7620,7 @@
         <v>38</v>
       </c>
       <c r="D317" t="s" s="2">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E317" s="2"/>
     </row>
@@ -7599,7 +7665,7 @@
         <v>38</v>
       </c>
       <c r="D320" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E320" s="2"/>
     </row>
@@ -7629,7 +7695,7 @@
         <v>38</v>
       </c>
       <c r="D322" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E322" s="2"/>
     </row>
@@ -7644,7 +7710,7 @@
         <v>38</v>
       </c>
       <c r="D323" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E323" s="2"/>
     </row>
@@ -7674,7 +7740,7 @@
         <v>38</v>
       </c>
       <c r="D325" t="s" s="2">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E325" s="2"/>
     </row>
@@ -7689,7 +7755,7 @@
         <v>38</v>
       </c>
       <c r="D326" t="s" s="2">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E326" s="2"/>
     </row>
@@ -7764,7 +7830,7 @@
         <v>38</v>
       </c>
       <c r="D331" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E331" s="2"/>
     </row>
@@ -7779,7 +7845,7 @@
         <v>38</v>
       </c>
       <c r="D332" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E332" s="2"/>
     </row>
@@ -7884,7 +7950,7 @@
         <v>38</v>
       </c>
       <c r="D339" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E339" s="2"/>
     </row>
@@ -7899,7 +7965,7 @@
         <v>38</v>
       </c>
       <c r="D340" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E340" s="2"/>
     </row>
@@ -7959,7 +8025,7 @@
         <v>38</v>
       </c>
       <c r="D344" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E344" s="2"/>
     </row>
@@ -7974,7 +8040,7 @@
         <v>38</v>
       </c>
       <c r="D345" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E345" s="2"/>
     </row>
@@ -8019,7 +8085,7 @@
         <v>38</v>
       </c>
       <c r="D348" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E348" s="2"/>
     </row>
@@ -8094,7 +8160,7 @@
         <v>38</v>
       </c>
       <c r="D353" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E353" s="2"/>
     </row>
@@ -8124,7 +8190,7 @@
         <v>38</v>
       </c>
       <c r="D355" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E355" s="2"/>
     </row>
@@ -8154,7 +8220,7 @@
         <v>38</v>
       </c>
       <c r="D357" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E357" s="2"/>
     </row>
@@ -8169,7 +8235,7 @@
         <v>38</v>
       </c>
       <c r="D358" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E358" s="2"/>
     </row>
@@ -8184,7 +8250,7 @@
         <v>38</v>
       </c>
       <c r="D359" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E359" s="2"/>
     </row>
@@ -8199,7 +8265,7 @@
         <v>38</v>
       </c>
       <c r="D360" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E360" s="2"/>
     </row>
@@ -8214,7 +8280,7 @@
         <v>38</v>
       </c>
       <c r="D361" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E361" s="2"/>
     </row>
@@ -8229,7 +8295,7 @@
         <v>38</v>
       </c>
       <c r="D362" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E362" s="2"/>
     </row>
@@ -8334,7 +8400,7 @@
         <v>38</v>
       </c>
       <c r="D369" t="s" s="2">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="E369" s="2"/>
     </row>
@@ -8424,7 +8490,7 @@
         <v>38</v>
       </c>
       <c r="D375" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E375" s="2"/>
     </row>
@@ -8454,7 +8520,7 @@
         <v>38</v>
       </c>
       <c r="D377" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E377" s="2"/>
     </row>
@@ -8469,7 +8535,7 @@
         <v>38</v>
       </c>
       <c r="D378" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E378" s="2"/>
     </row>
@@ -8499,7 +8565,7 @@
         <v>38</v>
       </c>
       <c r="D380" t="s" s="2">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="E380" s="2"/>
     </row>
@@ -8514,7 +8580,7 @@
         <v>38</v>
       </c>
       <c r="D381" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E381" s="2"/>
     </row>
@@ -8544,9 +8610,174 @@
         <v>38</v>
       </c>
       <c r="D383" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E383" s="2"/>
+    </row>
+    <row r="384">
+      <c r="A384" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="B384" t="s" s="2">
+        <v>805</v>
+      </c>
+      <c r="C384" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D384" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E384" s="2"/>
+    </row>
+    <row r="385">
+      <c r="A385" t="s" s="2">
+        <v>806</v>
+      </c>
+      <c r="B385" t="s" s="2">
+        <v>807</v>
+      </c>
+      <c r="C385" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D385" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E385" s="2"/>
+    </row>
+    <row r="386">
+      <c r="A386" t="s" s="2">
+        <v>808</v>
+      </c>
+      <c r="B386" t="s" s="2">
+        <v>809</v>
+      </c>
+      <c r="C386" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D386" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="E386" s="2"/>
+    </row>
+    <row r="387">
+      <c r="A387" t="s" s="2">
+        <v>810</v>
+      </c>
+      <c r="B387" t="s" s="2">
+        <v>811</v>
+      </c>
+      <c r="C387" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D387" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E387" s="2"/>
+    </row>
+    <row r="388">
+      <c r="A388" t="s" s="2">
+        <v>812</v>
+      </c>
+      <c r="B388" t="s" s="2">
+        <v>813</v>
+      </c>
+      <c r="C388" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D388" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="E388" s="2"/>
+    </row>
+    <row r="389">
+      <c r="A389" t="s" s="2">
+        <v>814</v>
+      </c>
+      <c r="B389" t="s" s="2">
+        <v>815</v>
+      </c>
+      <c r="C389" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D389" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E389" s="2"/>
+    </row>
+    <row r="390">
+      <c r="A390" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="B390" t="s" s="2">
+        <v>817</v>
+      </c>
+      <c r="C390" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D390" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="E390" s="2"/>
+    </row>
+    <row r="391">
+      <c r="A391" t="s" s="2">
+        <v>818</v>
+      </c>
+      <c r="B391" t="s" s="2">
+        <v>819</v>
+      </c>
+      <c r="C391" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D391" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E391" s="2"/>
+    </row>
+    <row r="392">
+      <c r="A392" t="s" s="2">
+        <v>820</v>
+      </c>
+      <c r="B392" t="s" s="2">
+        <v>821</v>
+      </c>
+      <c r="C392" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D392" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="E392" s="2"/>
+    </row>
+    <row r="393">
+      <c r="A393" t="s" s="2">
+        <v>822</v>
+      </c>
+      <c r="B393" t="s" s="2">
+        <v>823</v>
+      </c>
+      <c r="C393" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D393" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E393" s="2"/>
+    </row>
+    <row r="394">
+      <c r="A394" t="s" s="2">
+        <v>824</v>
+      </c>
+      <c r="B394" t="s" s="2">
+        <v>825</v>
+      </c>
+      <c r="C394" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D394" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="E394" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -8577,7 +8808,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>804</v>
+        <v>826</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>34</v>
@@ -8594,55 +8825,55 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>805</v>
+        <v>827</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>806</v>
+        <v>828</v>
       </c>
       <c r="C3" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>807</v>
+        <v>829</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>808</v>
+        <v>830</v>
       </c>
       <c r="C4" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>809</v>
+        <v>831</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>810</v>
+        <v>832</v>
       </c>
       <c r="C5" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>811</v>
+        <v>833</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>812</v>
+        <v>834</v>
       </c>
       <c r="C6" t="s" s="2">
         <v>38</v>
@@ -8654,16 +8885,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>813</v>
+        <v>835</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>814</v>
+        <v>836</v>
       </c>
       <c r="C7" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="E7" s="2"/>
     </row>
@@ -8696,7 +8927,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>815</v>
+        <v>837</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>34</v>
@@ -8713,10 +8944,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>816</v>
+        <v>838</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>817</v>
+        <v>839</v>
       </c>
       <c r="C3" t="s" s="2">
         <v>38</v>
@@ -8728,10 +8959,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>818</v>
+        <v>840</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>819</v>
+        <v>841</v>
       </c>
       <c r="C4" t="s" s="2">
         <v>38</v>
@@ -8743,10 +8974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>820</v>
+        <v>842</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>821</v>
+        <v>843</v>
       </c>
       <c r="C5" t="s" s="2">
         <v>38</v>
@@ -8758,10 +8989,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>822</v>
+        <v>844</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>823</v>
+        <v>845</v>
       </c>
       <c r="C6" t="s" s="2">
         <v>38</v>
@@ -8773,10 +9004,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>824</v>
+        <v>846</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>825</v>
+        <v>847</v>
       </c>
       <c r="C7" t="s" s="2">
         <v>38</v>
@@ -8788,10 +9019,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>826</v>
+        <v>848</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>827</v>
+        <v>849</v>
       </c>
       <c r="C8" t="s" s="2">
         <v>38</v>
@@ -8803,10 +9034,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>828</v>
+        <v>850</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>829</v>
+        <v>851</v>
       </c>
       <c r="C9" t="s" s="2">
         <v>38</v>
@@ -8818,10 +9049,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>830</v>
+        <v>852</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>831</v>
+        <v>853</v>
       </c>
       <c r="C10" t="s" s="2">
         <v>38</v>
@@ -8833,10 +9064,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>832</v>
+        <v>854</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>833</v>
+        <v>855</v>
       </c>
       <c r="C11" t="s" s="2">
         <v>38</v>
@@ -8848,10 +9079,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>834</v>
+        <v>856</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>835</v>
+        <v>857</v>
       </c>
       <c r="C12" t="s" s="2">
         <v>38</v>

--- a/ig/ch-elm/ch-elm-results-to-foph-patient-name-representation.xlsx
+++ b/ig/ch-elm/ch-elm-results-to-foph-patient-name-representation.xlsx
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.15.0</t>
+    <t>1.15.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T07:20:00+00:00</t>
+    <t>2026-08-14T07:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
